--- a/product_upload/packages/27/file.xlsx
+++ b/product_upload/packages/27/file.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AT101"/>
+  <dimension ref="A1:AU101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -596,7 +596,7 @@
       </c>
       <c r="AJ1" t="inlineStr">
         <is>
-          <t>Manufacture Name</t>
+          <t>Manufacturer Name</t>
         </is>
       </c>
       <c r="AK1" t="inlineStr">
@@ -645,6 +645,11 @@
         </is>
       </c>
       <c r="AT1" t="inlineStr">
+        <is>
+          <t>Name / En</t>
+        </is>
+      </c>
+      <c r="AU1" t="inlineStr">
         <is>
           <t>Seller SKU</t>
         </is>
@@ -669,7 +674,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -844,6 +849,11 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
+          <t>ANXETIN 20MG CAPSULES</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
           <t>SKU-263A55CE0775</t>
         </is>
       </c>
@@ -867,7 +877,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -1030,6 +1040,11 @@
       <c r="AS3" t="inlineStr"/>
       <c r="AT3" t="inlineStr">
         <is>
+          <t>APHRODIL 50 mg Film coated tablet</t>
+        </is>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
           <t>SKU-0AA692F61092</t>
         </is>
       </c>
@@ -1053,7 +1068,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -1216,6 +1231,11 @@
       <c r="AS4" t="inlineStr"/>
       <c r="AT4" t="inlineStr">
         <is>
+          <t>ASMAFORT 1MG\5ML SYRUP</t>
+        </is>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
           <t>SKU-63126D7C6230</t>
         </is>
       </c>
@@ -1239,7 +1259,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1398,6 +1418,11 @@
       <c r="AS5" t="inlineStr"/>
       <c r="AT5" t="inlineStr">
         <is>
+          <t>ASMAFORT 1MGTAB</t>
+        </is>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
           <t>SKU-04E20A123659</t>
         </is>
       </c>
@@ -1421,7 +1446,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1580,6 +1605,11 @@
       <c r="AS6" t="inlineStr"/>
       <c r="AT6" t="inlineStr">
         <is>
+          <t>AMLOPRESS 5MG CAPSULES</t>
+        </is>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
           <t>SKU-2AD5D229DB8A</t>
         </is>
       </c>
@@ -1603,7 +1633,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1778,6 +1808,11 @@
       <c r="AS7" t="inlineStr"/>
       <c r="AT7" t="inlineStr">
         <is>
+          <t>ADOL 125 MG RECTAL SUPPOSITORIES</t>
+        </is>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
           <t>SKU-D3462A3A44CB</t>
         </is>
       </c>
@@ -1801,7 +1836,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1964,6 +1999,11 @@
       <c r="AS8" t="inlineStr"/>
       <c r="AT8" t="inlineStr">
         <is>
+          <t>ADOL 250 MG RECTAL SUUPPOSITORIES</t>
+        </is>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
           <t>SKU-2EA5EFDF9A3E</t>
         </is>
       </c>
@@ -1987,7 +2027,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -2158,6 +2198,11 @@
       <c r="AS9" t="inlineStr"/>
       <c r="AT9" t="inlineStr">
         <is>
+          <t>ADOL 500 MG RECTAL SUPPOSITORIES</t>
+        </is>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
           <t>SKU-7C28BFFBE866</t>
         </is>
       </c>
@@ -2181,7 +2226,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -2360,6 +2405,11 @@
       <c r="AS10" t="inlineStr"/>
       <c r="AT10" t="inlineStr">
         <is>
+          <t>ADOL 500MG CAPLET</t>
+        </is>
+      </c>
+      <c r="AU10" t="inlineStr">
+        <is>
           <t>SKU-B143EC40312B</t>
         </is>
       </c>
@@ -2383,7 +2433,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -2546,6 +2596,11 @@
       <c r="AS11" t="inlineStr"/>
       <c r="AT11" t="inlineStr">
         <is>
+          <t>ADOL ALLERGY SINUS 325MG-2MG-30MG CAPLET</t>
+        </is>
+      </c>
+      <c r="AU11" t="inlineStr">
+        <is>
           <t>SKU-33FA605887C2</t>
         </is>
       </c>
@@ -2569,7 +2624,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -2732,6 +2787,11 @@
       <c r="AS12" t="inlineStr"/>
       <c r="AT12" t="inlineStr">
         <is>
+          <t>ADOL COLD CAPLET</t>
+        </is>
+      </c>
+      <c r="AU12" t="inlineStr">
+        <is>
           <t>SKU-98039CD90FC9</t>
         </is>
       </c>
@@ -2755,7 +2815,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -2926,6 +2986,11 @@
       <c r="AS13" t="inlineStr"/>
       <c r="AT13" t="inlineStr">
         <is>
+          <t>ADOL DROPS 100MG-ML</t>
+        </is>
+      </c>
+      <c r="AU13" t="inlineStr">
+        <is>
           <t>SKU-B9A5E311B492</t>
         </is>
       </c>
@@ -2949,7 +3014,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -3112,6 +3177,11 @@
       <c r="AS14" t="inlineStr"/>
       <c r="AT14" t="inlineStr">
         <is>
+          <t>ADOL PM 325MG-25MG CAPLET</t>
+        </is>
+      </c>
+      <c r="AU14" t="inlineStr">
+        <is>
           <t>SKU-ECAFBC35CC26</t>
         </is>
       </c>
@@ -3135,7 +3205,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -3310,6 +3380,11 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
+          <t>ADOL SYRUP 120MG-5ML</t>
+        </is>
+      </c>
+      <c r="AU15" t="inlineStr">
+        <is>
           <t>SKU-7E4705981A19</t>
         </is>
       </c>
@@ -3333,7 +3408,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Oman</t>
+          <t>OM</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -3496,6 +3571,11 @@
       <c r="AS16" t="inlineStr"/>
       <c r="AT16" t="inlineStr">
         <is>
+          <t>ADVAQUIN 500MG FILM COATED TABLET</t>
+        </is>
+      </c>
+      <c r="AU16" t="inlineStr">
+        <is>
           <t>SKU-320BC63E10E9</t>
         </is>
       </c>
@@ -3519,7 +3599,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -3678,6 +3758,11 @@
       <c r="AS17" t="inlineStr"/>
       <c r="AT17" t="inlineStr">
         <is>
+          <t>ALBENDA 100MG\5ML SUSP</t>
+        </is>
+      </c>
+      <c r="AU17" t="inlineStr">
+        <is>
           <t>SKU-BCB44CA835C2</t>
         </is>
       </c>
@@ -3701,7 +3786,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -3876,6 +3961,11 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
+          <t>ALFACORT 1% CREAM</t>
+        </is>
+      </c>
+      <c r="AU18" t="inlineStr">
+        <is>
           <t>SKU-BAD76FC45102</t>
         </is>
       </c>
@@ -3899,7 +3989,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -4074,6 +4164,11 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
+          <t>ALFACORT 1% OINTMENT</t>
+        </is>
+      </c>
+      <c r="AU19" t="inlineStr">
+        <is>
           <t>SKU-D048567B5FEC</t>
         </is>
       </c>
@@ -4097,7 +4192,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -4260,6 +4355,11 @@
       <c r="AS20" t="inlineStr"/>
       <c r="AT20" t="inlineStr">
         <is>
+          <t>AMOLAR 10MG CAPSULES</t>
+        </is>
+      </c>
+      <c r="AU20" t="inlineStr">
+        <is>
           <t>SKU-D7170A59A321</t>
         </is>
       </c>
@@ -4283,7 +4383,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -4458,6 +4558,11 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
+          <t>AMLOPHAR 5MG CAPSULES</t>
+        </is>
+      </c>
+      <c r="AU21" t="inlineStr">
+        <is>
           <t>SKU-D70226F20AE8</t>
         </is>
       </c>
@@ -4481,7 +4586,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -4656,6 +4761,11 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
+          <t>ADOL SINUS 325MG-30MG CAPLET</t>
+        </is>
+      </c>
+      <c r="AU22" t="inlineStr">
+        <is>
           <t>SKU-4BEB9280E8CA</t>
         </is>
       </c>
@@ -4679,7 +4789,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -4854,6 +4964,11 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
+          <t>CAPOCARD 25MG TAB</t>
+        </is>
+      </c>
+      <c r="AU23" t="inlineStr">
+        <is>
           <t>SKU-E2F1F7D3BAD4</t>
         </is>
       </c>
@@ -4877,7 +4992,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -5052,6 +5167,11 @@
       </c>
       <c r="AT24" t="inlineStr">
         <is>
+          <t>CAPOCARD 50MG TAB</t>
+        </is>
+      </c>
+      <c r="AU24" t="inlineStr">
+        <is>
           <t>SKU-186FDA6720D3</t>
         </is>
       </c>
@@ -5075,7 +5195,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -5250,6 +5370,11 @@
       </c>
       <c r="AT25" t="inlineStr">
         <is>
+          <t>CARBATOL 200MG TAB</t>
+        </is>
+      </c>
+      <c r="AU25" t="inlineStr">
+        <is>
           <t>SKU-DE414E8DE062</t>
         </is>
       </c>
@@ -5273,7 +5398,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Oman</t>
+          <t>OM</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -5440,6 +5565,11 @@
       <c r="AS26" t="inlineStr"/>
       <c r="AT26" t="inlineStr">
         <is>
+          <t>CEFIM 100 POWDER FOR ORAL SUSPENTION</t>
+        </is>
+      </c>
+      <c r="AU26" t="inlineStr">
+        <is>
           <t>SKU-355071A892F2</t>
         </is>
       </c>
@@ -5463,7 +5593,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Oman</t>
+          <t>OM</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -5626,6 +5756,11 @@
       <c r="AS27" t="inlineStr"/>
       <c r="AT27" t="inlineStr">
         <is>
+          <t>CEFOVEX 500MG TABLET</t>
+        </is>
+      </c>
+      <c r="AU27" t="inlineStr">
+        <is>
           <t>SKU-A77C0F3A9FB8</t>
         </is>
       </c>
@@ -5649,7 +5784,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -5816,6 +5951,11 @@
       </c>
       <c r="AT28" t="inlineStr">
         <is>
+          <t>LEXEK 125MG-5ML SUSP</t>
+        </is>
+      </c>
+      <c r="AU28" t="inlineStr">
+        <is>
           <t>SKU-18A18F63A9EC</t>
         </is>
       </c>
@@ -5839,7 +5979,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -6002,6 +6142,11 @@
       <c r="AS29" t="inlineStr"/>
       <c r="AT29" t="inlineStr">
         <is>
+          <t>LEXEK 250MG-5ML SUSP</t>
+        </is>
+      </c>
+      <c r="AU29" t="inlineStr">
+        <is>
           <t>SKU-8A29868285C5</t>
         </is>
       </c>
@@ -6025,7 +6170,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -6188,6 +6333,11 @@
       <c r="AS30" t="inlineStr"/>
       <c r="AT30" t="inlineStr">
         <is>
+          <t>Lexek 500MG CAPS</t>
+        </is>
+      </c>
+      <c r="AU30" t="inlineStr">
+        <is>
           <t>SKU-B5D3C842774C</t>
         </is>
       </c>
@@ -6211,7 +6361,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -6378,6 +6528,11 @@
       </c>
       <c r="AT31" t="inlineStr">
         <is>
+          <t>CEFUZIME 125MG-5ML POWDER FOR ORAL SUSP</t>
+        </is>
+      </c>
+      <c r="AU31" t="inlineStr">
+        <is>
           <t>SKU-3302EB977D04</t>
         </is>
       </c>
@@ -6401,7 +6556,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -6564,6 +6719,11 @@
       <c r="AS32" t="inlineStr"/>
       <c r="AT32" t="inlineStr">
         <is>
+          <t>CEFUZIME 250MG TAB.</t>
+        </is>
+      </c>
+      <c r="AU32" t="inlineStr">
+        <is>
           <t>SKU-514DD3924803</t>
         </is>
       </c>
@@ -6587,7 +6747,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -6754,6 +6914,11 @@
       </c>
       <c r="AT33" t="inlineStr">
         <is>
+          <t>CEFUZIME 500 MG TAB</t>
+        </is>
+      </c>
+      <c r="AU33" t="inlineStr">
+        <is>
           <t>SKU-2EB36C179F93</t>
         </is>
       </c>
@@ -6777,7 +6942,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -6952,6 +7117,11 @@
       </c>
       <c r="AT34" t="inlineStr">
         <is>
+          <t>CEPHADAR FORTE</t>
+        </is>
+      </c>
+      <c r="AU34" t="inlineStr">
+        <is>
           <t>SKU-7BBF11CAFE74</t>
         </is>
       </c>
@@ -6975,7 +7145,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -7138,6 +7308,11 @@
       <c r="AS35" t="inlineStr"/>
       <c r="AT35" t="inlineStr">
         <is>
+          <t>CETRALON 10 MG TAB</t>
+        </is>
+      </c>
+      <c r="AU35" t="inlineStr">
+        <is>
           <t>SKU-71B0B73183A2</t>
         </is>
       </c>
@@ -7161,7 +7336,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -7328,6 +7503,11 @@
       </c>
       <c r="AT36" t="inlineStr">
         <is>
+          <t>CETRALON 5MG-5ML SYRUP</t>
+        </is>
+      </c>
+      <c r="AU36" t="inlineStr">
+        <is>
           <t>SKU-B1C648E87196</t>
         </is>
       </c>
@@ -7351,7 +7531,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -7522,6 +7702,11 @@
       <c r="AS37" t="inlineStr"/>
       <c r="AT37" t="inlineStr">
         <is>
+          <t>LEXEK 250MG CAPS</t>
+        </is>
+      </c>
+      <c r="AU37" t="inlineStr">
+        <is>
           <t>SKU-4DDC58750FDE</t>
         </is>
       </c>
@@ -7545,7 +7730,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -7708,6 +7893,11 @@
       <c r="AS38" t="inlineStr"/>
       <c r="AT38" t="inlineStr">
         <is>
+          <t>3V TABLETS</t>
+        </is>
+      </c>
+      <c r="AU38" t="inlineStr">
+        <is>
           <t>SKU-A93940F7AB91</t>
         </is>
       </c>
@@ -7731,7 +7921,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -7898,6 +8088,11 @@
       </c>
       <c r="AT39" t="inlineStr">
         <is>
+          <t>BUTALIN TABS 4MG</t>
+        </is>
+      </c>
+      <c r="AU39" t="inlineStr">
+        <is>
           <t>SKU-FDB143424AD8</t>
         </is>
       </c>
@@ -7921,7 +8116,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -8088,6 +8283,11 @@
       <c r="AS40" t="inlineStr"/>
       <c r="AT40" t="inlineStr">
         <is>
+          <t>BUTALIN SYRUP 2MG-5ML</t>
+        </is>
+      </c>
+      <c r="AU40" t="inlineStr">
+        <is>
           <t>SKU-63ACDB1D702F</t>
         </is>
       </c>
@@ -8111,7 +8311,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -8278,6 +8478,11 @@
       </c>
       <c r="AT41" t="inlineStr">
         <is>
+          <t>AZOMAX 250MG CAPSULE</t>
+        </is>
+      </c>
+      <c r="AU41" t="inlineStr">
+        <is>
           <t>SKU-CDEAE03EF58F</t>
         </is>
       </c>
@@ -8301,7 +8506,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -8468,6 +8673,11 @@
       <c r="AS42" t="inlineStr"/>
       <c r="AT42" t="inlineStr">
         <is>
+          <t>AZOMYCIN 200MG\5ML SUSP.</t>
+        </is>
+      </c>
+      <c r="AU42" t="inlineStr">
+        <is>
           <t>SKU-069184993B35</t>
         </is>
       </c>
@@ -8491,7 +8701,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -8658,6 +8868,11 @@
       <c r="AS43" t="inlineStr"/>
       <c r="AT43" t="inlineStr">
         <is>
+          <t>AZOMYCIN 200MG\5ML SUSP.</t>
+        </is>
+      </c>
+      <c r="AU43" t="inlineStr">
+        <is>
           <t>SKU-3B7D9D9E2442</t>
         </is>
       </c>
@@ -8681,7 +8896,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -8848,6 +9063,11 @@
       </c>
       <c r="AT44" t="inlineStr">
         <is>
+          <t>BUTALIN 2 mg tablet</t>
+        </is>
+      </c>
+      <c r="AU44" t="inlineStr">
+        <is>
           <t>SKU-2650BE931DBE</t>
         </is>
       </c>
@@ -8871,7 +9091,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -9038,6 +9258,11 @@
       </c>
       <c r="AT45" t="inlineStr">
         <is>
+          <t>BETASONE 0.1% CREAM</t>
+        </is>
+      </c>
+      <c r="AU45" t="inlineStr">
+        <is>
           <t>SKU-562FF61935C2</t>
         </is>
       </c>
@@ -9061,7 +9286,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -9236,6 +9461,11 @@
       </c>
       <c r="AT46" t="inlineStr">
         <is>
+          <t>BETASONE 500MCG TAB</t>
+        </is>
+      </c>
+      <c r="AU46" t="inlineStr">
+        <is>
           <t>SKU-CC0A24B398B2</t>
         </is>
       </c>
@@ -9259,7 +9489,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -9430,6 +9660,11 @@
       <c r="AS47" t="inlineStr"/>
       <c r="AT47" t="inlineStr">
         <is>
+          <t>BUTALIN 0.5% SOLUTION FOR NEBULISER</t>
+        </is>
+      </c>
+      <c r="AU47" t="inlineStr">
+        <is>
           <t>SKU-2795C3BA094E</t>
         </is>
       </c>
@@ -9453,7 +9688,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -9620,6 +9855,11 @@
       <c r="AS48" t="inlineStr"/>
       <c r="AT48" t="inlineStr">
         <is>
+          <t>BUTALIN 100MCG-DOSE INHALER</t>
+        </is>
+      </c>
+      <c r="AU48" t="inlineStr">
+        <is>
           <t>SKU-114F43D318CF</t>
         </is>
       </c>
@@ -9643,7 +9883,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -9810,6 +10050,11 @@
       </c>
       <c r="AT49" t="inlineStr">
         <is>
+          <t>BETASONE 0.1% OINTMENT</t>
+        </is>
+      </c>
+      <c r="AU49" t="inlineStr">
+        <is>
           <t>SKU-91D72E64FF0B</t>
         </is>
       </c>
@@ -9833,7 +10078,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -10000,6 +10245,11 @@
       </c>
       <c r="AT50" t="inlineStr">
         <is>
+          <t>ESPERAL 300 mg Film Coated Tablet</t>
+        </is>
+      </c>
+      <c r="AU50" t="inlineStr">
+        <is>
           <t>SKU-B5257A5C9B0F</t>
         </is>
       </c>
@@ -10023,7 +10273,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -10194,6 +10444,11 @@
       <c r="AS51" t="inlineStr"/>
       <c r="AT51" t="inlineStr">
         <is>
+          <t>TELFAST 120 MG FILM COATED TAB</t>
+        </is>
+      </c>
+      <c r="AU51" t="inlineStr">
+        <is>
           <t>SKU-1B4CC9A36FAB</t>
         </is>
       </c>
@@ -10217,7 +10472,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -10384,6 +10639,11 @@
       </c>
       <c r="AT52" t="inlineStr">
         <is>
+          <t>ATOXIA 120 mg Film-coated Tablet</t>
+        </is>
+      </c>
+      <c r="AU52" t="inlineStr">
+        <is>
           <t>SKU-40FD1107A33F</t>
         </is>
       </c>
@@ -10407,7 +10667,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -10574,6 +10834,11 @@
       </c>
       <c r="AT53" t="inlineStr">
         <is>
+          <t>ARBAVAL 320 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU53" t="inlineStr">
+        <is>
           <t>SKU-838CFF58CC79</t>
         </is>
       </c>
@@ -10597,7 +10862,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -10760,6 +11025,11 @@
       <c r="AS54" t="inlineStr"/>
       <c r="AT54" t="inlineStr">
         <is>
+          <t>ARBAVAL PLUS</t>
+        </is>
+      </c>
+      <c r="AU54" t="inlineStr">
+        <is>
           <t>SKU-1C711A3F5C79</t>
         </is>
       </c>
@@ -10783,7 +11053,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -10946,6 +11216,11 @@
       <c r="AS55" t="inlineStr"/>
       <c r="AT55" t="inlineStr">
         <is>
+          <t>ARBAVAL PLUS</t>
+        </is>
+      </c>
+      <c r="AU55" t="inlineStr">
+        <is>
           <t>SKU-47A9E477F95C</t>
         </is>
       </c>
@@ -10969,7 +11244,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -11132,6 +11407,11 @@
       <c r="AS56" t="inlineStr"/>
       <c r="AT56" t="inlineStr">
         <is>
+          <t>ARBAVAL PLUS</t>
+        </is>
+      </c>
+      <c r="AU56" t="inlineStr">
+        <is>
           <t>SKU-897203664783</t>
         </is>
       </c>
@@ -11155,7 +11435,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -11318,6 +11598,11 @@
       <c r="AS57" t="inlineStr"/>
       <c r="AT57" t="inlineStr">
         <is>
+          <t>ZOLIX 5 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU57" t="inlineStr">
+        <is>
           <t>SKU-99755EA444AA</t>
         </is>
       </c>
@@ -11341,7 +11626,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -11504,6 +11789,11 @@
       <c r="AS58" t="inlineStr"/>
       <c r="AT58" t="inlineStr">
         <is>
+          <t>NEUROGAB 150 mg capsule</t>
+        </is>
+      </c>
+      <c r="AU58" t="inlineStr">
+        <is>
           <t>SKU-7200D8A86291</t>
         </is>
       </c>
@@ -11527,7 +11817,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -11702,6 +11992,11 @@
       </c>
       <c r="AT59" t="inlineStr">
         <is>
+          <t>LETARA 2.5 mg tablet</t>
+        </is>
+      </c>
+      <c r="AU59" t="inlineStr">
+        <is>
           <t>SKU-2DE51501D6AB</t>
         </is>
       </c>
@@ -11725,7 +12020,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -11900,6 +12195,11 @@
       </c>
       <c r="AT60" t="inlineStr">
         <is>
+          <t>MOXIFLOX 400 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU60" t="inlineStr">
+        <is>
           <t>SKU-A3948BCC3C4E</t>
         </is>
       </c>
@@ -11923,7 +12223,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -12090,6 +12390,11 @@
       <c r="AS61" t="inlineStr"/>
       <c r="AT61" t="inlineStr">
         <is>
+          <t>MOXIFLOX 400 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU61" t="inlineStr">
+        <is>
           <t>SKU-1635BAEB053B</t>
         </is>
       </c>
@@ -12113,7 +12418,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -12292,6 +12597,11 @@
       </c>
       <c r="AT62" t="inlineStr">
         <is>
+          <t>LANOXIN 0.05MG-ML ELIXIR</t>
+        </is>
+      </c>
+      <c r="AU62" t="inlineStr">
+        <is>
           <t>SKU-8E3BDECD8AC0</t>
         </is>
       </c>
@@ -12315,7 +12625,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -12482,6 +12792,11 @@
       </c>
       <c r="AT63" t="inlineStr">
         <is>
+          <t>DESTAMIN 5 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU63" t="inlineStr">
+        <is>
           <t>SKU-A29977157CC7</t>
         </is>
       </c>
@@ -12505,7 +12820,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -12680,6 +12995,11 @@
       </c>
       <c r="AT64" t="inlineStr">
         <is>
+          <t>NORMATEC 20 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU64" t="inlineStr">
+        <is>
           <t>SKU-F2ABC45DEC36</t>
         </is>
       </c>
@@ -12703,7 +13023,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -12874,6 +13194,11 @@
       <c r="AS65" t="inlineStr"/>
       <c r="AT65" t="inlineStr">
         <is>
+          <t>NORMATEC 40 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU65" t="inlineStr">
+        <is>
           <t>SKU-7241C7FD3B77</t>
         </is>
       </c>
@@ -12897,7 +13222,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -13064,6 +13389,11 @@
       </c>
       <c r="AT66" t="inlineStr">
         <is>
+          <t>ARBAVAL 160 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU66" t="inlineStr">
+        <is>
           <t>SKU-59D2016B04E2</t>
         </is>
       </c>
@@ -13087,7 +13417,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -13246,6 +13576,11 @@
       <c r="AS67" t="inlineStr"/>
       <c r="AT67" t="inlineStr">
         <is>
+          <t>ARBAVAL 80 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU67" t="inlineStr">
+        <is>
           <t>SKU-44C5B3D0C508</t>
         </is>
       </c>
@@ -13269,7 +13604,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -13436,6 +13771,11 @@
       </c>
       <c r="AT68" t="inlineStr">
         <is>
+          <t>ARBAVAL 40 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU68" t="inlineStr">
+        <is>
           <t>SKU-C5A98C280FDA</t>
         </is>
       </c>
@@ -13459,7 +13799,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -13630,6 +13970,11 @@
       <c r="AS69" t="inlineStr"/>
       <c r="AT69" t="inlineStr">
         <is>
+          <t>LEVAQUIN 500 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU69" t="inlineStr">
+        <is>
           <t>SKU-D8D26B054EF9</t>
         </is>
       </c>
@@ -13653,7 +13998,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -13828,6 +14173,11 @@
       </c>
       <c r="AT70" t="inlineStr">
         <is>
+          <t>BUTAFYL 1% cream</t>
+        </is>
+      </c>
+      <c r="AU70" t="inlineStr">
+        <is>
           <t>SKU-3E7317AC3019</t>
         </is>
       </c>
@@ -13851,7 +14201,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -14026,6 +14376,11 @@
       </c>
       <c r="AT71" t="inlineStr">
         <is>
+          <t>AMAGLIME 1 mg tablet</t>
+        </is>
+      </c>
+      <c r="AU71" t="inlineStr">
+        <is>
           <t>SKU-810E51EB0AF9</t>
         </is>
       </c>
@@ -14049,7 +14404,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -14212,6 +14567,11 @@
       <c r="AS72" t="inlineStr"/>
       <c r="AT72" t="inlineStr">
         <is>
+          <t>AMAGLIME 1 mg tablet</t>
+        </is>
+      </c>
+      <c r="AU72" t="inlineStr">
+        <is>
           <t>SKU-5FAE6A897BBB</t>
         </is>
       </c>
@@ -14235,7 +14595,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -14406,6 +14766,11 @@
       <c r="AS73" t="inlineStr"/>
       <c r="AT73" t="inlineStr">
         <is>
+          <t>AMAGLIME 2 mg tablet</t>
+        </is>
+      </c>
+      <c r="AU73" t="inlineStr">
+        <is>
           <t>SKU-41F9F62F8A4F</t>
         </is>
       </c>
@@ -14429,7 +14794,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -14604,6 +14969,11 @@
       </c>
       <c r="AT74" t="inlineStr">
         <is>
+          <t>AMAGLIME 3 mg tablet</t>
+        </is>
+      </c>
+      <c r="AU74" t="inlineStr">
+        <is>
           <t>SKU-CE8EFB10198A</t>
         </is>
       </c>
@@ -14627,7 +14997,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -14794,6 +15164,11 @@
       </c>
       <c r="AT75" t="inlineStr">
         <is>
+          <t>AMAGLIME 3 mg tablet</t>
+        </is>
+      </c>
+      <c r="AU75" t="inlineStr">
+        <is>
           <t>SKU-A8B1790DE2B4</t>
         </is>
       </c>
@@ -14817,7 +15192,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -14988,6 +15363,11 @@
       <c r="AS76" t="inlineStr"/>
       <c r="AT76" t="inlineStr">
         <is>
+          <t>CLOVIRAX 5% cream</t>
+        </is>
+      </c>
+      <c r="AU76" t="inlineStr">
+        <is>
           <t>SKU-4077BD29A19D</t>
         </is>
       </c>
@@ -15011,7 +15391,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -15186,6 +15566,11 @@
       </c>
       <c r="AT77" t="inlineStr">
         <is>
+          <t>CLOVIRAX 5% cream</t>
+        </is>
+      </c>
+      <c r="AU77" t="inlineStr">
+        <is>
           <t>SKU-131FFEE5CF36</t>
         </is>
       </c>
@@ -15209,7 +15594,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -15376,6 +15761,11 @@
       </c>
       <c r="AT78" t="inlineStr">
         <is>
+          <t>LYRGABA 75 mg capsule</t>
+        </is>
+      </c>
+      <c r="AU78" t="inlineStr">
+        <is>
           <t>SKU-EF7F818ED895</t>
         </is>
       </c>
@@ -15399,7 +15789,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -15566,6 +15956,11 @@
       </c>
       <c r="AT79" t="inlineStr">
         <is>
+          <t>LYRGABA 75 mg capsule</t>
+        </is>
+      </c>
+      <c r="AU79" t="inlineStr">
+        <is>
           <t>SKU-AB0A1F93CD07</t>
         </is>
       </c>
@@ -15589,7 +15984,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -15752,6 +16147,11 @@
       <c r="AS80" t="inlineStr"/>
       <c r="AT80" t="inlineStr">
         <is>
+          <t>LYRGABA 150 mg capsule</t>
+        </is>
+      </c>
+      <c r="AU80" t="inlineStr">
+        <is>
           <t>SKU-1A4A5089D39C</t>
         </is>
       </c>
@@ -15775,7 +16175,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -15950,6 +16350,11 @@
       </c>
       <c r="AT81" t="inlineStr">
         <is>
+          <t>NORMATEC PLUS 40/12.5 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU81" t="inlineStr">
+        <is>
           <t>SKU-7BC7DEA66400</t>
         </is>
       </c>
@@ -15973,7 +16378,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -16140,6 +16545,11 @@
       </c>
       <c r="AT82" t="inlineStr">
         <is>
+          <t>LYRGABA 150 mg capsule</t>
+        </is>
+      </c>
+      <c r="AU82" t="inlineStr">
+        <is>
           <t>SKU-48E3C0C34044</t>
         </is>
       </c>
@@ -16163,7 +16573,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -16330,6 +16740,11 @@
       <c r="AS83" t="inlineStr"/>
       <c r="AT83" t="inlineStr">
         <is>
+          <t>DUETACT 30/4 mg tablet</t>
+        </is>
+      </c>
+      <c r="AU83" t="inlineStr">
+        <is>
           <t>SKU-ADBD03EEC379</t>
         </is>
       </c>
@@ -16353,7 +16768,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -16524,6 +16939,11 @@
       <c r="AS84" t="inlineStr"/>
       <c r="AT84" t="inlineStr">
         <is>
+          <t>DUETACT 30/2 mg tablet</t>
+        </is>
+      </c>
+      <c r="AU84" t="inlineStr">
+        <is>
           <t>SKU-20202F3F5ED4</t>
         </is>
       </c>
@@ -16547,7 +16967,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -16710,6 +17130,11 @@
       <c r="AS85" t="inlineStr"/>
       <c r="AT85" t="inlineStr">
         <is>
+          <t>LEVACIN 750 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU85" t="inlineStr">
+        <is>
           <t>SKU-F2A8F763B542</t>
         </is>
       </c>
@@ -16733,7 +17158,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -16904,6 +17329,11 @@
       <c r="AS86" t="inlineStr"/>
       <c r="AT86" t="inlineStr">
         <is>
+          <t>GLANDY 60 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU86" t="inlineStr">
+        <is>
           <t>SKU-2F0B4EF909DA</t>
         </is>
       </c>
@@ -16927,7 +17357,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -17094,6 +17524,11 @@
       </c>
       <c r="AT87" t="inlineStr">
         <is>
+          <t>10% DEXTROSE W/V intravenous infusion</t>
+        </is>
+      </c>
+      <c r="AU87" t="inlineStr">
+        <is>
           <t>SKU-27825FBC18A7</t>
         </is>
       </c>
@@ -17117,7 +17552,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -17288,6 +17723,11 @@
       <c r="AS88" t="inlineStr"/>
       <c r="AT88" t="inlineStr">
         <is>
+          <t>MEMAXIA 10 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU88" t="inlineStr">
+        <is>
           <t>SKU-7F3C71F4C994</t>
         </is>
       </c>
@@ -17311,7 +17751,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -17478,6 +17918,11 @@
       </c>
       <c r="AT89" t="inlineStr">
         <is>
+          <t>ALLAIR 4 mg chewable tablet</t>
+        </is>
+      </c>
+      <c r="AU89" t="inlineStr">
+        <is>
           <t>SKU-1625D76CAFF1</t>
         </is>
       </c>
@@ -17501,7 +17946,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -17664,6 +18109,11 @@
       <c r="AS90" t="inlineStr"/>
       <c r="AT90" t="inlineStr">
         <is>
+          <t>ALLAIR 5 mg chewable tablet</t>
+        </is>
+      </c>
+      <c r="AU90" t="inlineStr">
+        <is>
           <t>SKU-617CA715608A</t>
         </is>
       </c>
@@ -17687,7 +18137,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -17858,6 +18308,11 @@
       <c r="AS91" t="inlineStr"/>
       <c r="AT91" t="inlineStr">
         <is>
+          <t>ACTOSMET 15/850 mg tablet</t>
+        </is>
+      </c>
+      <c r="AU91" t="inlineStr">
+        <is>
           <t>SKU-1BAEA7F734C5</t>
         </is>
       </c>
@@ -17881,7 +18336,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -18056,6 +18511,11 @@
       </c>
       <c r="AT92" t="inlineStr">
         <is>
+          <t>NORMATEC PLUS 20/12.5 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU92" t="inlineStr">
+        <is>
           <t>SKU-F78F3C306DC8</t>
         </is>
       </c>
@@ -18079,7 +18539,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -18250,6 +18710,11 @@
       <c r="AS93" t="inlineStr"/>
       <c r="AT93" t="inlineStr">
         <is>
+          <t>NORMATEC PLUS 40/25 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU93" t="inlineStr">
+        <is>
           <t>SKU-DB9E0477C3EA</t>
         </is>
       </c>
@@ -18273,7 +18738,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -18440,6 +18905,11 @@
       </c>
       <c r="AT94" t="inlineStr">
         <is>
+          <t>VFONAZ 50 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU94" t="inlineStr">
+        <is>
           <t>SKU-FF5BEC1DB32C</t>
         </is>
       </c>
@@ -18463,7 +18933,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -18630,6 +19100,11 @@
       <c r="AS95" t="inlineStr"/>
       <c r="AT95" t="inlineStr">
         <is>
+          <t>QUETTA XR 300 mg tablet</t>
+        </is>
+      </c>
+      <c r="AU95" t="inlineStr">
+        <is>
           <t>SKU-35B535FAF731</t>
         </is>
       </c>
@@ -18653,7 +19128,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -18824,6 +19299,11 @@
       <c r="AS96" t="inlineStr"/>
       <c r="AT96" t="inlineStr">
         <is>
+          <t>QUETTA XR 400 mg tablet</t>
+        </is>
+      </c>
+      <c r="AU96" t="inlineStr">
+        <is>
           <t>SKU-0FBF4B44F289</t>
         </is>
       </c>
@@ -18847,7 +19327,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -19018,6 +19498,11 @@
       <c r="AS97" t="inlineStr"/>
       <c r="AT97" t="inlineStr">
         <is>
+          <t>AMODIP 5 mg capsule</t>
+        </is>
+      </c>
+      <c r="AU97" t="inlineStr">
+        <is>
           <t>SKU-11DFE12DB4B8</t>
         </is>
       </c>
@@ -19041,7 +19526,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -19216,6 +19701,11 @@
       </c>
       <c r="AT98" t="inlineStr">
         <is>
+          <t>AVOBAN 2% nasal ointment</t>
+        </is>
+      </c>
+      <c r="AU98" t="inlineStr">
+        <is>
           <t>SKU-5DAC9D26826C</t>
         </is>
       </c>
@@ -19239,7 +19729,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -19410,6 +19900,11 @@
       <c r="AS99" t="inlineStr"/>
       <c r="AT99" t="inlineStr">
         <is>
+          <t>ATOZET 10/10 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU99" t="inlineStr">
+        <is>
           <t>SKU-AB2FFF6CCE98</t>
         </is>
       </c>
@@ -19433,7 +19928,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -19604,6 +20099,11 @@
       <c r="AS100" t="inlineStr"/>
       <c r="AT100" t="inlineStr">
         <is>
+          <t>ATOZET 10/20 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU100" t="inlineStr">
+        <is>
           <t>SKU-DECDC30274B5</t>
         </is>
       </c>
@@ -19627,7 +20127,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -19797,6 +20297,11 @@
       </c>
       <c r="AS101" t="inlineStr"/>
       <c r="AT101" t="inlineStr">
+        <is>
+          <t>ATOZET 10/40 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU101" t="inlineStr">
         <is>
           <t>SKU-9D81BFCB1331</t>
         </is>
@@ -19813,7 +20318,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB12"/>
+  <dimension ref="A1:AC12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19859,100 +20364,105 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
+          <t>Manufacturer Name</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
           <t>Seller SKU</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>price</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Level 1*</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Level 2*</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Level 3*</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Risk Class *</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Sterility</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Brand</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Model / Catalogue Number</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Single Use</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Legal Manufacturer</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>UDI-DI</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>GMDN Code / Term</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>SFDA Authorized Representative License No.</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Size</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>Power Source</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>Warranty</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>Storage Conditions / En</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>Usage Instructions</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>Branch id</t>
         </is>
@@ -19984,7 +20494,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -19999,92 +20509,97 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>SKU-83822</t>
         </is>
       </c>
-      <c r="J2" t="n">
+      <c r="K2" t="n">
         <v>340.75</v>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T2" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U2" t="inlineStr">
+      <c r="U2" t="n">
+        <v>197</v>
+      </c>
+      <c r="V2" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W2" t="n">
+      <c r="X2" t="n">
         <v>100</v>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y2" t="n">
+      <c r="Z2" t="n">
         <v>12</v>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="AA2" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20116,7 +20631,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -20131,92 +20646,97 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>SKU-53349</t>
         </is>
       </c>
-      <c r="J3" t="n">
+      <c r="K3" t="n">
         <v>80.16</v>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T3" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U3" t="inlineStr">
+      <c r="U3" t="n">
+        <v>198</v>
+      </c>
+      <c r="V3" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W3" t="n">
+      <c r="X3" t="n">
         <v>100</v>
       </c>
-      <c r="X3" t="inlineStr">
+      <c r="Y3" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y3" t="n">
+      <c r="Z3" t="n">
         <v>12</v>
       </c>
-      <c r="Z3" t="inlineStr">
+      <c r="AA3" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA3" t="inlineStr">
+      <c r="AB3" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20248,7 +20768,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -20263,92 +20783,97 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>SKU-33556</t>
         </is>
       </c>
-      <c r="J4" t="n">
+      <c r="K4" t="n">
         <v>497.44</v>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T4" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U4" t="inlineStr">
+      <c r="U4" t="n">
+        <v>199</v>
+      </c>
+      <c r="V4" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W4" t="n">
+      <c r="X4" t="n">
         <v>100</v>
       </c>
-      <c r="X4" t="inlineStr">
+      <c r="Y4" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y4" t="n">
+      <c r="Z4" t="n">
         <v>12</v>
       </c>
-      <c r="Z4" t="inlineStr">
+      <c r="AA4" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA4" t="inlineStr">
+      <c r="AB4" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
+      <c r="AC4" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20380,7 +20905,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -20395,92 +20920,97 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>SKU-85833</t>
         </is>
       </c>
-      <c r="J5" t="n">
+      <c r="K5" t="n">
         <v>318.58</v>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T5" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U5" t="inlineStr">
+      <c r="U5" t="n">
+        <v>200</v>
+      </c>
+      <c r="V5" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W5" t="n">
+      <c r="X5" t="n">
         <v>100</v>
       </c>
-      <c r="X5" t="inlineStr">
+      <c r="Y5" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y5" t="n">
+      <c r="Z5" t="n">
         <v>12</v>
       </c>
-      <c r="Z5" t="inlineStr">
+      <c r="AA5" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA5" t="inlineStr">
+      <c r="AB5" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20512,7 +21042,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -20527,92 +21057,97 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>SKU-81738</t>
         </is>
       </c>
-      <c r="J6" t="n">
+      <c r="K6" t="n">
         <v>389.03</v>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T6" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U6" t="inlineStr">
+      <c r="U6" t="n">
+        <v>201</v>
+      </c>
+      <c r="V6" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W6" t="n">
+      <c r="X6" t="n">
         <v>100</v>
       </c>
-      <c r="X6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y6" t="n">
+      <c r="Z6" t="n">
         <v>12</v>
       </c>
-      <c r="Z6" t="inlineStr">
+      <c r="AA6" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA6" t="inlineStr">
+      <c r="AB6" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
+      <c r="AC6" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20644,7 +21179,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -20659,92 +21194,97 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>SKU-88268</t>
         </is>
       </c>
-      <c r="J7" t="n">
+      <c r="K7" t="n">
         <v>360.15</v>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="R7" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T7" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U7" t="inlineStr">
+      <c r="U7" t="n">
+        <v>202</v>
+      </c>
+      <c r="V7" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W7" t="n">
+      <c r="X7" t="n">
         <v>100</v>
       </c>
-      <c r="X7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y7" t="n">
+      <c r="Z7" t="n">
         <v>12</v>
       </c>
-      <c r="Z7" t="inlineStr">
+      <c r="AA7" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA7" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20776,7 +21316,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -20791,92 +21331,97 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>SKU-87370</t>
         </is>
       </c>
-      <c r="J8" t="n">
+      <c r="K8" t="n">
         <v>292.51</v>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="R8" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T8" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U8" t="inlineStr">
+      <c r="U8" t="n">
+        <v>203</v>
+      </c>
+      <c r="V8" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W8" t="n">
+      <c r="X8" t="n">
         <v>100</v>
       </c>
-      <c r="X8" t="inlineStr">
+      <c r="Y8" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y8" t="n">
+      <c r="Z8" t="n">
         <v>12</v>
       </c>
-      <c r="Z8" t="inlineStr">
+      <c r="AA8" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA8" t="inlineStr">
+      <c r="AB8" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
+      <c r="AC8" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20908,7 +21453,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -20923,92 +21468,97 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>SKU-74503</t>
         </is>
       </c>
-      <c r="J9" t="n">
+      <c r="K9" t="n">
         <v>156.65</v>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="Q9" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
+      <c r="R9" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T9" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U9" t="inlineStr">
+      <c r="U9" t="n">
+        <v>204</v>
+      </c>
+      <c r="V9" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W9" t="n">
+      <c r="X9" t="n">
         <v>100</v>
       </c>
-      <c r="X9" t="inlineStr">
+      <c r="Y9" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y9" t="n">
+      <c r="Z9" t="n">
         <v>12</v>
       </c>
-      <c r="Z9" t="inlineStr">
+      <c r="AA9" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA9" t="inlineStr">
+      <c r="AB9" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
+      <c r="AC9" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -21040,7 +21590,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -21055,92 +21605,97 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
           <t>SKU-68882</t>
         </is>
       </c>
-      <c r="J10" t="n">
+      <c r="K10" t="n">
         <v>342.79</v>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="Q10" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr">
+      <c r="R10" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T10" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U10" t="inlineStr">
+      <c r="U10" t="n">
+        <v>205</v>
+      </c>
+      <c r="V10" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W10" t="n">
+      <c r="X10" t="n">
         <v>100</v>
       </c>
-      <c r="X10" t="inlineStr">
+      <c r="Y10" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y10" t="n">
+      <c r="Z10" t="n">
         <v>12</v>
       </c>
-      <c r="Z10" t="inlineStr">
+      <c r="AA10" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA10" t="inlineStr">
+      <c r="AB10" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
+      <c r="AC10" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -21172,7 +21727,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -21187,92 +21742,97 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
           <t>SKU-42969</t>
         </is>
       </c>
-      <c r="J11" t="n">
+      <c r="K11" t="n">
         <v>175.59</v>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="N11" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="O11" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
+      <c r="P11" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
+      <c r="Q11" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr">
+      <c r="R11" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T11" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U11" t="inlineStr">
+      <c r="U11" t="n">
+        <v>206</v>
+      </c>
+      <c r="V11" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W11" t="n">
+      <c r="X11" t="n">
         <v>100</v>
       </c>
-      <c r="X11" t="inlineStr">
+      <c r="Y11" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y11" t="n">
+      <c r="Z11" t="n">
         <v>12</v>
       </c>
-      <c r="Z11" t="inlineStr">
+      <c r="AA11" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA11" t="inlineStr">
+      <c r="AB11" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
+      <c r="AC11" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -21304,7 +21864,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -21319,92 +21879,97 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
           <t>SKU-87731</t>
         </is>
       </c>
-      <c r="J12" t="n">
+      <c r="K12" t="n">
         <v>109.2</v>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>Medical Devices</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>Diabetic Care</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="P12" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
+      <c r="Q12" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr">
+      <c r="R12" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T12" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U12" t="inlineStr">
+      <c r="U12" t="n">
+        <v>207</v>
+      </c>
+      <c r="V12" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W12" t="n">
+      <c r="X12" t="n">
         <v>100</v>
       </c>
-      <c r="X12" t="inlineStr">
+      <c r="Y12" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y12" t="n">
+      <c r="Z12" t="n">
         <v>12</v>
       </c>
-      <c r="Z12" t="inlineStr">
+      <c r="AA12" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA12" t="inlineStr">
+      <c r="AB12" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
+      <c r="AC12" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -21421,7 +21986,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W14"/>
+  <dimension ref="A1:Y14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21537,6 +22102,16 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
+          <t>Manufacturer Name</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>Ingredients</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
           <t>Seller SKU</t>
         </is>
       </c>
@@ -21572,7 +22147,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -21647,6 +22222,16 @@
         </is>
       </c>
       <c r="W2" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
         <is>
           <t>SKU-9BA2D0EFA4FA</t>
         </is>
@@ -21683,7 +22268,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -21758,6 +22343,16 @@
         </is>
       </c>
       <c r="W3" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
         <is>
           <t>SKU-9752B35CEEEC</t>
         </is>
@@ -21794,7 +22389,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -21869,6 +22464,16 @@
         </is>
       </c>
       <c r="W4" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
         <is>
           <t>SKU-90D0C8826548</t>
         </is>
@@ -21905,7 +22510,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -21980,6 +22585,16 @@
         </is>
       </c>
       <c r="W5" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
         <is>
           <t>SKU-C80BDCD6B5EF</t>
         </is>
@@ -22016,7 +22631,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -22091,6 +22706,16 @@
         </is>
       </c>
       <c r="W6" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
         <is>
           <t>SKU-6F62085D90AC</t>
         </is>
@@ -22127,7 +22752,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -22202,6 +22827,16 @@
         </is>
       </c>
       <c r="W7" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
         <is>
           <t>SKU-A96DA9DDE180</t>
         </is>
@@ -22238,7 +22873,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -22313,6 +22948,16 @@
         </is>
       </c>
       <c r="W8" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
         <is>
           <t>SKU-F2C160D68F81</t>
         </is>
@@ -22349,7 +22994,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -22424,6 +23069,16 @@
         </is>
       </c>
       <c r="W9" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
         <is>
           <t>SKU-2C76DDCE7CEF</t>
         </is>
@@ -22460,7 +23115,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -22535,6 +23190,16 @@
         </is>
       </c>
       <c r="W10" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
         <is>
           <t>SKU-48ED7238543C</t>
         </is>
@@ -22571,7 +23236,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -22646,6 +23311,16 @@
         </is>
       </c>
       <c r="W11" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
         <is>
           <t>SKU-3621441F2412</t>
         </is>
@@ -22682,7 +23357,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -22757,6 +23432,16 @@
         </is>
       </c>
       <c r="W12" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
         <is>
           <t>SKU-06B7D749B781</t>
         </is>
@@ -22793,7 +23478,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -22868,6 +23553,16 @@
         </is>
       </c>
       <c r="W13" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
         <is>
           <t>SKU-AE646B4B392F</t>
         </is>
@@ -22904,7 +23599,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -22979,6 +23674,16 @@
         </is>
       </c>
       <c r="W14" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
         <is>
           <t>SKU-F0F5A97FF336</t>
         </is>

--- a/product_upload/packages/27/file.xlsx
+++ b/product_upload/packages/27/file.xlsx
@@ -885,8 +885,16 @@
           <t>8279210487-257-592678571679</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ APHRODIL 50 mg Film coated tablet</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>APHRODIL 50 mg Film coated tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I3" t="inlineStr">
         <is>
           <t>0</t>
@@ -1076,8 +1084,16 @@
           <t>1454953798-560-838991515663</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ASMAFORT 1MG\5ML SYRUP</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>ASMAFORT 1MG\5ML SYRUP detailed description.</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr">
         <is>
           <t>0</t>
@@ -1267,8 +1283,16 @@
           <t>5660588129-424-734375523861</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ASMAFORT 1MGTAB</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>ASMAFORT 1MGTAB detailed description.</t>
+        </is>
+      </c>
       <c r="I5" t="inlineStr">
         <is>
           <t>0</t>
@@ -1454,8 +1478,16 @@
           <t>5790831253-629-511276265487</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ AMLOPRESS 5MG CAPSULES</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>AMLOPRESS 5MG CAPSULES detailed description.</t>
+        </is>
+      </c>
       <c r="I6" t="inlineStr">
         <is>
           <t>0</t>
@@ -1844,8 +1876,16 @@
           <t>1646813441-262-099142388624</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ADOL 250 MG RECTAL SUUPPOSITORIES</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>ADOL 250 MG RECTAL SUUPPOSITORIES detailed description.</t>
+        </is>
+      </c>
       <c r="I8" t="inlineStr">
         <is>
           <t>0</t>
@@ -2441,8 +2481,16 @@
           <t>0167471630-091-960908585032</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ADOL ALLERGY SINUS 325MG-2MG-30MG CAPLET</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>ADOL ALLERGY SINUS 325MG-2MG-30MG CAPLET detailed description.</t>
+        </is>
+      </c>
       <c r="I11" t="inlineStr">
         <is>
           <t>0</t>
@@ -2632,8 +2680,16 @@
           <t>5790209829-505-615018811562</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ADOL COLD CAPLET</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>ADOL COLD CAPLET detailed description.</t>
+        </is>
+      </c>
       <c r="I12" t="inlineStr">
         <is>
           <t>0</t>
@@ -3022,8 +3078,16 @@
           <t>2378282969-658-668878391542</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ADOL PM 325MG-25MG CAPLET</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>ADOL PM 325MG-25MG CAPLET detailed description.</t>
+        </is>
+      </c>
       <c r="I14" t="inlineStr">
         <is>
           <t>0</t>
@@ -3416,8 +3480,16 @@
           <t>9235520855-888-457520329985</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ADVAQUIN 500MG FILM COATED TABLET</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>ADVAQUIN 500MG FILM COATED TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I16" t="inlineStr">
         <is>
           <t>0</t>
@@ -3607,8 +3679,16 @@
           <t>6252214151-622-556848358870</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ALBENDA 100MG\5ML SUSP</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>ALBENDA 100MG\5ML SUSP detailed description.</t>
+        </is>
+      </c>
       <c r="I17" t="inlineStr">
         <is>
           <t>0</t>
@@ -4200,8 +4280,16 @@
           <t>5064265131-913-395697824960</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ AMOLAR 10MG CAPSULES</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>AMOLAR 10MG CAPSULES detailed description.</t>
+        </is>
+      </c>
       <c r="I20" t="inlineStr">
         <is>
           <t>0</t>
@@ -5601,8 +5689,16 @@
           <t>2637572686-919-421318939948</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CEFOVEX 500MG TABLET</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>CEFOVEX 500MG TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I27" t="inlineStr">
         <is>
           <t>0</t>
@@ -5792,8 +5888,16 @@
           <t>2842374668-502-633764500515</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ LEXEK 125MG-5ML SUSP</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>LEXEK 125MG-5ML SUSP detailed description.</t>
+        </is>
+      </c>
       <c r="I28" t="inlineStr">
         <is>
           <t>0</t>
@@ -5987,8 +6091,16 @@
           <t>8611144597-904-691248524356</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ LEXEK 250MG-5ML SUSP</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>LEXEK 250MG-5ML SUSP detailed description.</t>
+        </is>
+      </c>
       <c r="I29" t="inlineStr">
         <is>
           <t>0</t>
@@ -6178,8 +6290,16 @@
           <t>1013398233-594-697548683639</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Lexek 500MG CAPS</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Lexek 500MG CAPS detailed description.</t>
+        </is>
+      </c>
       <c r="I30" t="inlineStr">
         <is>
           <t>0</t>
@@ -6369,8 +6489,16 @@
           <t>9488376403-712-814114470804</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CEFUZIME 125MG-5ML POWDER FOR ORAL SUSP</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>CEFUZIME 125MG-5ML POWDER FOR ORAL SUSP detailed description.</t>
+        </is>
+      </c>
       <c r="I31" t="inlineStr">
         <is>
           <t>0</t>
@@ -6564,8 +6692,16 @@
           <t>6869388170-141-558711610964</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CEFUZIME 250MG TAB.</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>CEFUZIME 250MG TAB. detailed description.</t>
+        </is>
+      </c>
       <c r="I32" t="inlineStr">
         <is>
           <t>0</t>
@@ -6755,8 +6891,16 @@
           <t>5438135868-746-407337190707</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CEFUZIME 500 MG TAB</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>CEFUZIME 500 MG TAB detailed description.</t>
+        </is>
+      </c>
       <c r="I33" t="inlineStr">
         <is>
           <t>0</t>
@@ -7153,8 +7297,16 @@
           <t>6175321784-046-360546757651</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr"/>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CETRALON 10 MG TAB</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>CETRALON 10 MG TAB detailed description.</t>
+        </is>
+      </c>
       <c r="I35" t="inlineStr">
         <is>
           <t>0</t>
@@ -7344,8 +7496,16 @@
           <t>8486349422-549-104367653646</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr"/>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CETRALON 5MG-5ML SYRUP</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>CETRALON 5MG-5ML SYRUP detailed description.</t>
+        </is>
+      </c>
       <c r="I36" t="inlineStr">
         <is>
           <t>0</t>
@@ -7738,8 +7898,16 @@
           <t>9707974959-494-210570655916</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr"/>
-      <c r="H38" t="inlineStr"/>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ 3V TABLETS</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>3V TABLETS detailed description.</t>
+        </is>
+      </c>
       <c r="I38" t="inlineStr">
         <is>
           <t>0</t>
@@ -7929,8 +8097,16 @@
           <t>2227586120-037-660314261350</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr"/>
-      <c r="H39" t="inlineStr"/>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ BUTALIN TABS 4MG</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>BUTALIN TABS 4MG detailed description.</t>
+        </is>
+      </c>
       <c r="I39" t="inlineStr">
         <is>
           <t>0</t>
@@ -8319,8 +8495,16 @@
           <t>0741029864-249-685129341051</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr"/>
-      <c r="H41" t="inlineStr"/>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ AZOMAX 250MG CAPSULE</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>AZOMAX 250MG CAPSULE detailed description.</t>
+        </is>
+      </c>
       <c r="I41" t="inlineStr">
         <is>
           <t>0</t>
@@ -8904,8 +9088,16 @@
           <t>4119661499-860-955850687030</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr"/>
-      <c r="H44" t="inlineStr"/>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ BUTALIN 2 mg tablet</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>BUTALIN 2 mg tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I44" t="inlineStr">
         <is>
           <t>0</t>
@@ -9099,8 +9291,16 @@
           <t>7870804589-822-744495701101</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr"/>
-      <c r="H45" t="inlineStr"/>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ BETASONE 0.1% CREAM</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>BETASONE 0.1% CREAM detailed description.</t>
+        </is>
+      </c>
       <c r="I45" t="inlineStr">
         <is>
           <t>0</t>
@@ -9891,8 +10091,16 @@
           <t>2757922569-685-721626028689</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr"/>
-      <c r="H49" t="inlineStr"/>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ BETASONE 0.1% OINTMENT</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>BETASONE 0.1% OINTMENT detailed description.</t>
+        </is>
+      </c>
       <c r="I49" t="inlineStr">
         <is>
           <t>0</t>
@@ -10086,8 +10294,16 @@
           <t>6340233577-935-762978253311</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr"/>
-      <c r="H50" t="inlineStr"/>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ESPERAL 300 mg Film Coated Tablet</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>ESPERAL 300 mg Film Coated Tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I50" t="inlineStr">
         <is>
           <t>0</t>
@@ -10480,8 +10696,16 @@
           <t>3583952270-635-815380202485</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr"/>
-      <c r="H52" t="inlineStr"/>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ATOXIA 120 mg Film-coated Tablet</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>ATOXIA 120 mg Film-coated Tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I52" t="inlineStr">
         <is>
           <t xml:space="preserve">MS Pharma Saudi </t>
@@ -10675,8 +10899,16 @@
           <t>2307796951-870-768411731085</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr"/>
-      <c r="H53" t="inlineStr"/>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ARBAVAL 320 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>ARBAVAL 320 mg film-coated tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I53" t="inlineStr">
         <is>
           <t>0</t>
@@ -10870,8 +11102,16 @@
           <t>6746693100-230-019296268023</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr"/>
-      <c r="H54" t="inlineStr"/>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ARBAVAL PLUS</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>ARBAVAL PLUS detailed description.</t>
+        </is>
+      </c>
       <c r="I54" t="inlineStr">
         <is>
           <t>0</t>
@@ -11061,8 +11301,16 @@
           <t>0901424906-292-794617335169</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr"/>
-      <c r="H55" t="inlineStr"/>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ARBAVAL PLUS</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>ARBAVAL PLUS detailed description.</t>
+        </is>
+      </c>
       <c r="I55" t="inlineStr">
         <is>
           <t>0</t>
@@ -11252,8 +11500,16 @@
           <t>6330919918-937-329938490576</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr"/>
-      <c r="H56" t="inlineStr"/>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ARBAVAL PLUS</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>ARBAVAL PLUS detailed description.</t>
+        </is>
+      </c>
       <c r="I56" t="inlineStr">
         <is>
           <t>0</t>
@@ -11443,8 +11699,16 @@
           <t>5663641750-700-051673680604</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr"/>
-      <c r="H57" t="inlineStr"/>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ZOLIX 5 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>ZOLIX 5 mg film-coated tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I57" t="inlineStr">
         <is>
           <t>0</t>
@@ -11634,8 +11898,16 @@
           <t>7442246861-213-343668555466</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr"/>
-      <c r="H58" t="inlineStr"/>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ NEUROGAB 150 mg capsule</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>NEUROGAB 150 mg capsule detailed description.</t>
+        </is>
+      </c>
       <c r="I58" t="inlineStr">
         <is>
           <t>0</t>
@@ -12633,8 +12905,16 @@
           <t>5459463406-813-005713601806</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr"/>
-      <c r="H63" t="inlineStr"/>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ DESTAMIN 5 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>DESTAMIN 5 mg film-coated tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I63" t="inlineStr">
         <is>
           <t>0</t>
@@ -13230,8 +13510,16 @@
           <t>8184950223-256-513842076144</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr"/>
-      <c r="H66" t="inlineStr"/>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ARBAVAL 160 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>ARBAVAL 160 mg film-coated tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I66" t="inlineStr">
         <is>
           <t>0</t>
@@ -13425,8 +13713,16 @@
           <t>1653689039-484-235820068498</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr"/>
-      <c r="H67" t="inlineStr"/>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ARBAVAL 80 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>ARBAVAL 80 mg film-coated tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I67" t="inlineStr">
         <is>
           <t>0</t>
@@ -13612,8 +13908,16 @@
           <t>3780151683-664-860470540335</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr"/>
-      <c r="H68" t="inlineStr"/>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ARBAVAL 40 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>ARBAVAL 40 mg film-coated tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I68" t="inlineStr">
         <is>
           <t>0</t>
@@ -14412,8 +14716,16 @@
           <t>5412878596-510-851830096213</t>
         </is>
       </c>
-      <c r="G72" t="inlineStr"/>
-      <c r="H72" t="inlineStr"/>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ AMAGLIME 1 mg tablet</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>AMAGLIME 1 mg tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I72" t="inlineStr">
         <is>
           <t>0</t>
@@ -15005,8 +15317,16 @@
           <t>7205624119-002-375469336611</t>
         </is>
       </c>
-      <c r="G75" t="inlineStr"/>
-      <c r="H75" t="inlineStr"/>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ AMAGLIME 3 mg tablet</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>AMAGLIME 3 mg tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I75" t="inlineStr">
         <is>
           <t>0</t>
@@ -15602,8 +15922,16 @@
           <t>6728204443-813-907973163461</t>
         </is>
       </c>
-      <c r="G78" t="inlineStr"/>
-      <c r="H78" t="inlineStr"/>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ LYRGABA 75 mg capsule</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>LYRGABA 75 mg capsule detailed description.</t>
+        </is>
+      </c>
       <c r="I78" t="inlineStr">
         <is>
           <t>0</t>
@@ -15797,8 +16125,16 @@
           <t>6803752211-557-475839732281</t>
         </is>
       </c>
-      <c r="G79" t="inlineStr"/>
-      <c r="H79" t="inlineStr"/>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ LYRGABA 75 mg capsule</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>LYRGABA 75 mg capsule detailed description.</t>
+        </is>
+      </c>
       <c r="I79" t="inlineStr">
         <is>
           <t>0</t>
@@ -15992,8 +16328,16 @@
           <t>4485735962-497-986992985041</t>
         </is>
       </c>
-      <c r="G80" t="inlineStr"/>
-      <c r="H80" t="inlineStr"/>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ LYRGABA 150 mg capsule</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>LYRGABA 150 mg capsule detailed description.</t>
+        </is>
+      </c>
       <c r="I80" t="inlineStr">
         <is>
           <t>0</t>
@@ -16386,8 +16730,16 @@
           <t>9024096653-841-263989107023</t>
         </is>
       </c>
-      <c r="G82" t="inlineStr"/>
-      <c r="H82" t="inlineStr"/>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ LYRGABA 150 mg capsule</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>LYRGABA 150 mg capsule detailed description.</t>
+        </is>
+      </c>
       <c r="I82" t="inlineStr">
         <is>
           <t>0</t>
@@ -16975,8 +17327,16 @@
           <t>3632878025-153-389952779582</t>
         </is>
       </c>
-      <c r="G85" t="inlineStr"/>
-      <c r="H85" t="inlineStr"/>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ LEVACIN 750 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>LEVACIN 750 mg film-coated tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I85" t="inlineStr">
         <is>
           <t>0</t>
@@ -17365,8 +17725,16 @@
           <t>0185985096-845-520896432061</t>
         </is>
       </c>
-      <c r="G87" t="inlineStr"/>
-      <c r="H87" t="inlineStr"/>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ 10% DEXTROSE W/V intravenous infusion</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>10% DEXTROSE W/V intravenous infusion detailed description.</t>
+        </is>
+      </c>
       <c r="I87" t="inlineStr">
         <is>
           <t>0</t>
@@ -17759,8 +18127,16 @@
           <t>9909652604-428-409301388745</t>
         </is>
       </c>
-      <c r="G89" t="inlineStr"/>
-      <c r="H89" t="inlineStr"/>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ALLAIR 4 mg chewable tablet</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>ALLAIR 4 mg chewable tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I89" t="inlineStr">
         <is>
           <t>0</t>
@@ -17954,8 +18330,16 @@
           <t>5838667709-398-758588777617</t>
         </is>
       </c>
-      <c r="G90" t="inlineStr"/>
-      <c r="H90" t="inlineStr"/>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ALLAIR 5 mg chewable tablet</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>ALLAIR 5 mg chewable tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I90" t="inlineStr">
         <is>
           <t>0</t>
@@ -18746,8 +19130,16 @@
           <t>1364147875-007-699380134296</t>
         </is>
       </c>
-      <c r="G94" t="inlineStr"/>
-      <c r="H94" t="inlineStr"/>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ VFONAZ 50 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>VFONAZ 50 mg film-coated tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I94" t="inlineStr">
         <is>
           <t>TABUK PHARMACEUTICAL MANUFACTURING CO.</t>

--- a/product_upload/packages/27/file.xlsx
+++ b/product_upload/packages/27/file.xlsx
@@ -596,7 +596,7 @@
       </c>
       <c r="AJ1" t="inlineStr">
         <is>
-          <t>Manufacturer Name</t>
+          <t>Manufacturer</t>
         </is>
       </c>
       <c r="AK1" t="inlineStr">
@@ -20756,7 +20756,7 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>Manufacturer Name</t>
+          <t>Manufacturer</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
@@ -22378,7 +22378,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y14"/>
+  <dimension ref="A1:Z14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22469,40 +22469,45 @@
       </c>
       <c r="R1" t="inlineStr">
         <is>
+          <t>Size unit</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
           <t>Manufacturer *</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>price</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t xml:space="preserve">Period After Opening </t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>Usage Instructions</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>Warnings</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
-        <is>
-          <t>Manufacturer Name</t>
-        </is>
-      </c>
       <c r="X1" t="inlineStr">
         <is>
+          <t>Manufacturer</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
           <t>Ingredients</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>Seller SKU</t>
         </is>
@@ -22592,38 +22597,43 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="S2" t="n">
+      <c r="T2" t="n">
         <v>149.47</v>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>SKU-9BA2D0EFA4FA</t>
         </is>
@@ -22713,38 +22723,43 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="S3" t="n">
+      <c r="T3" t="n">
         <v>256.04</v>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
+      <c r="Y3" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr">
+      <c r="Z3" t="inlineStr">
         <is>
           <t>SKU-9752B35CEEEC</t>
         </is>
@@ -22834,38 +22849,43 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="S4" t="n">
+      <c r="T4" t="n">
         <v>185.01</v>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
+      <c r="X4" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
+      <c r="Y4" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="Y4" t="inlineStr">
+      <c r="Z4" t="inlineStr">
         <is>
           <t>SKU-90D0C8826548</t>
         </is>
@@ -22955,38 +22975,43 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="S5" t="n">
+      <c r="T5" t="n">
         <v>224.92</v>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
+      <c r="X5" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
+      <c r="Y5" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="Y5" t="inlineStr">
+      <c r="Z5" t="inlineStr">
         <is>
           <t>SKU-C80BDCD6B5EF</t>
         </is>
@@ -23076,38 +23101,43 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="S6" t="n">
+      <c r="T6" t="n">
         <v>177.84</v>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
+      <c r="X6" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="Y6" t="inlineStr">
+      <c r="Z6" t="inlineStr">
         <is>
           <t>SKU-6F62085D90AC</t>
         </is>
@@ -23197,38 +23227,43 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="S7" t="n">
+      <c r="T7" t="n">
         <v>59.86</v>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
+      <c r="Z7" t="inlineStr">
         <is>
           <t>SKU-A96DA9DDE180</t>
         </is>
@@ -23318,38 +23353,43 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="S8" t="n">
+      <c r="T8" t="n">
         <v>91.84</v>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
+      <c r="Y8" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="Y8" t="inlineStr">
+      <c r="Z8" t="inlineStr">
         <is>
           <t>SKU-F2C160D68F81</t>
         </is>
@@ -23439,38 +23479,43 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="S9" t="n">
+      <c r="T9" t="n">
         <v>122.17</v>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
+      <c r="X9" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
+      <c r="Y9" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="Y9" t="inlineStr">
+      <c r="Z9" t="inlineStr">
         <is>
           <t>SKU-2C76DDCE7CEF</t>
         </is>
@@ -23560,38 +23605,43 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="S10" t="n">
+      <c r="T10" t="n">
         <v>216.5</v>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
+      <c r="X10" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr">
+      <c r="Y10" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="Y10" t="inlineStr">
+      <c r="Z10" t="inlineStr">
         <is>
           <t>SKU-48ED7238543C</t>
         </is>
@@ -23681,38 +23731,43 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="S11" t="n">
+      <c r="T11" t="n">
         <v>383.7</v>
       </c>
-      <c r="T11" t="inlineStr">
+      <c r="U11" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="V11" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
+      <c r="X11" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr">
+      <c r="Y11" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="Y11" t="inlineStr">
+      <c r="Z11" t="inlineStr">
         <is>
           <t>SKU-3621441F2412</t>
         </is>
@@ -23802,38 +23857,43 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="S12" t="n">
+      <c r="T12" t="n">
         <v>34.59</v>
       </c>
-      <c r="T12" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="U12" t="inlineStr">
+      <c r="V12" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
+      <c r="X12" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr">
+      <c r="Y12" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="Y12" t="inlineStr">
+      <c r="Z12" t="inlineStr">
         <is>
           <t>SKU-06B7D749B781</t>
         </is>
@@ -23923,38 +23983,43 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="S13" t="n">
+      <c r="T13" t="n">
         <v>188.38</v>
       </c>
-      <c r="T13" t="inlineStr">
+      <c r="U13" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="U13" t="inlineStr">
+      <c r="V13" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="V13" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
+      <c r="X13" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr">
+      <c r="Y13" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="Y13" t="inlineStr">
+      <c r="Z13" t="inlineStr">
         <is>
           <t>SKU-AE646B4B392F</t>
         </is>
@@ -24044,38 +24109,43 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="S14" t="n">
+      <c r="T14" t="n">
         <v>110.57</v>
       </c>
-      <c r="T14" t="inlineStr">
+      <c r="U14" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="U14" t="inlineStr">
+      <c r="V14" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="V14" t="inlineStr">
+      <c r="W14" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr">
+      <c r="X14" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr">
+      <c r="Y14" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="Y14" t="inlineStr">
+      <c r="Z14" t="inlineStr">
         <is>
           <t>SKU-F0F5A97FF336</t>
         </is>
